--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AD7A97-CAC3-4702-AE26-85A7A699DDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="23880" yWindow="4755" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="BOM_Board1_PCB1_2026-07-13" state="visible" r:id="rId4"/>
+    <sheet name="BOM_Board1_PCB1_2026-07-13" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="102">
   <si>
     <t>No.</t>
   </si>
@@ -265,21 +269,6 @@
     <t>C53223909</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>嘉立创二维码5x5</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>JLC-QRCODE-5x5</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>TYPE-C 6P</t>
   </si>
   <si>
@@ -292,9 +281,6 @@
     <t>C456012</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>16MHz</t>
   </si>
   <si>
@@ -311,19 +297,58 @@
   </si>
   <si>
     <t>C13738</t>
+  </si>
+  <si>
+    <t>A2541WR-4P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2 Hexagonal Copper Standoff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2*4+3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2 Screw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2 Nut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2*3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -346,11 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -686,14 +717,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="10" width="20" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="29.875" customWidth="1"/>
+    <col min="4" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -725,7 +758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -757,7 +790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -789,7 +822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -821,7 +854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -853,7 +886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -885,7 +918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -917,7 +950,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -949,7 +982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -981,7 +1014,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -1013,7 +1046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -1045,7 +1078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -1077,7 +1110,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -1109,7 +1142,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -1141,75 +1174,75 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>84</v>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>14</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
         <v>85</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>86</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s">
         <v>87</v>
       </c>
-      <c r="F15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" t="s">
-        <v>35</v>
-      </c>
       <c r="J15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>88</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A16" s="1">
+        <v>15</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
         <v>89</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>90</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
         <v>91</v>
       </c>
-      <c r="F16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" t="s">
-        <v>89</v>
-      </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
         <v>1</v>
       </c>
       <c r="C17" t="s">
@@ -1219,32 +1252,55 @@
         <v>95</v>
       </c>
       <c r="E17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
         <v>96</v>
       </c>
-      <c r="F17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="E18" t="s">
         <v>97</v>
       </c>
-      <c r="H17" t="s">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
         <v>98</v>
       </c>
-      <c r="I17" t="s">
+      <c r="E19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
         <v>99</v>
       </c>
-      <c r="J17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>35</v>
+      <c r="E20" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>